--- a/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497624021634</v>
+        <v>10.84497624874427</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907162134207</v>
+        <v>37.78907165105743</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.156539853331748</v>
+        <v>6.083890523217484</v>
       </c>
       <c r="C2" t="n">
-        <v>7.824529202847079</v>
+        <v>12.14029211071606</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98231284579033</v>
+        <v>25.64226828722244</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.95049600862693</v>
+        <v>19.23243752619501</v>
       </c>
       <c r="C3" t="n">
-        <v>38.36670028196535</v>
+        <v>42.89746593706438</v>
       </c>
       <c r="D3" t="n">
-        <v>46.53974991982005</v>
+        <v>77.6856958370501</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>35.69732827411827</v>
       </c>
       <c r="C4" t="n">
-        <v>60.77607337910305</v>
+        <v>82.71518932590652</v>
       </c>
       <c r="D4" t="n">
-        <v>58.13419030697488</v>
+        <v>81.7835107545763</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.54742397500478</v>
+        <v>45.7248993252952</v>
       </c>
       <c r="C5" t="n">
-        <v>117.7606371244049</v>
+        <v>125.7618809140164</v>
       </c>
       <c r="D5" t="n">
-        <v>45.18493808795945</v>
+        <v>55.14967728606459</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2933916371082</v>
+        <v>167.1651268452172</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>40.01014593887452</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8182257482527</v>
+        <v>185.5886042631128</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C8" t="n">
-        <v>103.0589652533089</v>
+        <v>133.9349305518711</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>53.80468293124643</v>
+        <v>64.34374453633593</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.672179883675971</v>
+        <v>7.615512221103435</v>
       </c>
       <c r="C21" t="n">
-        <v>93.02518108957115</v>
+        <v>91.38614665324121</v>
       </c>
       <c r="D21" t="n">
-        <v>7.672179883675971</v>
+        <v>7.615512221103435</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.300275928779282</v>
+        <v>6.167339078078462</v>
       </c>
       <c r="C2" t="n">
-        <v>14.71836158206818</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D2" t="n">
-        <v>33.55613653115598</v>
+        <v>27.93563092434299</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.62651926622549</v>
+        <v>19.40424337443821</v>
       </c>
       <c r="C3" t="n">
-        <v>34.11573272257666</v>
+        <v>44.57134577280519</v>
       </c>
       <c r="D3" t="n">
-        <v>52.02771958655972</v>
+        <v>79.0552338844744</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.11773727571416</v>
+        <v>35.33997210977243</v>
       </c>
       <c r="C4" t="n">
-        <v>77.25274509947727</v>
+        <v>93.71665409969629</v>
       </c>
       <c r="D4" t="n">
-        <v>66.62139921018856</v>
+        <v>97.74967366874218</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.57888095926969</v>
+        <v>48.67014243803564</v>
       </c>
       <c r="C5" t="n">
-        <v>114.889025089483</v>
+        <v>135.9966007307894</v>
       </c>
       <c r="D5" t="n">
-        <v>53.60342465187586</v>
+        <v>67.64241682260524</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.017722183068</v>
+        <v>51.84413276586557</v>
       </c>
       <c r="C6" t="n">
-        <v>165.7160672337489</v>
+        <v>180.1261600366836</v>
       </c>
       <c r="D6" t="n">
-        <v>43.39128503230054</v>
+        <v>46.73217246985243</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.9206269713388</v>
+        <v>40.06414206260808</v>
       </c>
       <c r="C7" t="n">
-        <v>181.0372219062246</v>
+        <v>211.4596197654247</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.03456645829366</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="C8" t="n">
-        <v>145.9515224518521</v>
+        <v>181.4171582677681</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>87.97343002985241</v>
+        <v>107.7203033530728</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>50.82016991033614</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.848544412687694</v>
+        <v>7.777038338815971</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0500093133541</v>
+        <v>99.15723881990363</v>
       </c>
       <c r="D21" t="n">
-        <v>8.829612464273657</v>
+        <v>8.749168131167966</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.301658587111028</v>
+        <v>6.503096792930871</v>
       </c>
       <c r="C2" t="n">
-        <v>10.6038569535698</v>
+        <v>11.32838675930394</v>
       </c>
       <c r="D2" t="n">
-        <v>30.87302005544945</v>
+        <v>25.64619527803943</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87333885061894</v>
+        <v>19.29625112697106</v>
       </c>
       <c r="C3" t="n">
-        <v>44.24246029188251</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D3" t="n">
-        <v>62.58641614573417</v>
+        <v>80.91073704550088</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.22434686484957</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="C4" t="n">
-        <v>79.72871280958772</v>
+        <v>99.58750537109221</v>
       </c>
       <c r="D4" t="n">
-        <v>73.83233609788137</v>
+        <v>108.3172059572548</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.24785205648926</v>
+        <v>49.67643383488862</v>
       </c>
       <c r="C5" t="n">
-        <v>125.2955507544992</v>
+        <v>148.8329519638165</v>
       </c>
       <c r="D5" t="n">
-        <v>62.68459091615885</v>
+        <v>81.75504007115315</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.82654342264714</v>
+        <v>56.63407981488576</v>
       </c>
       <c r="C6" t="n">
-        <v>173.4041335057056</v>
+        <v>194.6972594631147</v>
       </c>
       <c r="D6" t="n">
-        <v>48.38249036069132</v>
+        <v>53.65545728020094</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.84373185523806</v>
+        <v>47.9691745772034</v>
       </c>
       <c r="C7" t="n">
-        <v>204.8720926699286</v>
+        <v>229.7849224128957</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.21252483466959</v>
+        <v>30.87596529856218</v>
       </c>
       <c r="C8" t="n">
-        <v>185.0888946816511</v>
+        <v>219.4696992843744</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>15.75312366234431</v>
       </c>
       <c r="C9" t="n">
-        <v>127.3562391857132</v>
+        <v>152.3171745661883</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>69.46846755250431</v>
+        <v>79.8602670019568</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>42.11403126907541</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.007438942085235</v>
+        <v>7.921314811852151</v>
       </c>
       <c r="C21" t="n">
-        <v>108.1004257181507</v>
+        <v>105.9475856085225</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00929867760654</v>
+        <v>8.911479163333668</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.656650345420874</v>
+        <v>6.162430339557228</v>
       </c>
       <c r="C2" t="n">
-        <v>7.295367190258048</v>
+        <v>8.1563599268825</v>
       </c>
       <c r="D2" t="n">
-        <v>25.29865659073605</v>
+        <v>21.44824209468007</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.12921514852886</v>
+        <v>23.06616231127881</v>
       </c>
       <c r="C3" t="n">
-        <v>61.35923151542565</v>
+        <v>66.36123606856314</v>
       </c>
       <c r="D3" t="n">
-        <v>65.80163987714246</v>
+        <v>86.20726590991242</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.53369520267854</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C4" t="n">
-        <v>105.4073057618673</v>
+        <v>124.9597930396468</v>
       </c>
       <c r="D4" t="n">
-        <v>70.71823238001049</v>
+        <v>99.45987816954012</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>31.90680038802134</v>
       </c>
       <c r="C5" t="n">
-        <v>103.5989264906447</v>
+        <v>116.3371029532471</v>
       </c>
       <c r="D5" t="n">
-        <v>45.74944301790137</v>
+        <v>53.23526926278331</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>29.78622534684823</v>
       </c>
       <c r="C6" t="n">
-        <v>134.9235504900477</v>
+        <v>151.3462260866883</v>
       </c>
       <c r="D6" t="n">
-        <v>28.09565580013523</v>
+        <v>28.2566624236317</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>130.1336034410274</v>
+        <v>154.3277938644858</v>
       </c>
       <c r="D7" t="n">
-        <v>27.48795397120644</v>
+        <v>27.008861091534</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>112.2383062880166</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>60.90468232835936</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>27.90126975469435</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.25291535926396</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
         <v>17.5585576904542</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>6.052474596681584</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73104218676538</v>
+        <v>3.838633523605029</v>
       </c>
       <c r="C2" t="n">
-        <v>4.123340357836604</v>
+        <v>3.931899555508476</v>
       </c>
       <c r="D2" t="n">
-        <v>17.49376234197391</v>
+        <v>15.25046883776995</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.8557084496715</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C3" t="n">
-        <v>45.80834788015617</v>
+        <v>50.69745144730529</v>
       </c>
       <c r="D3" t="n">
-        <v>70.89691046218341</v>
+        <v>84.89663272474293</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>130.664728949025</v>
+        <v>147.7029603562284</v>
       </c>
       <c r="D4" t="n">
-        <v>83.69791877785757</v>
+        <v>114.1370063480299</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.41087892865646</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>146.3540390105933</v>
+        <v>164.7863521578271</v>
       </c>
       <c r="D5" t="n">
-        <v>56.91682315370885</v>
+        <v>68.52598975642738</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.63529824230149</v>
+        <v>34.61642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>153.600318815639</v>
+        <v>173.1626235704609</v>
       </c>
       <c r="D6" t="n">
-        <v>32.60384125803657</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>160.1966816404733</v>
+        <v>183.0134800348734</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>120.7500588838364</v>
+        <v>143.9487571351885</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>58.68593251676156</v>
+        <v>61.4593697812588</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>14.74977750860408</v>
@@ -2212,7 +2212,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.814490741626358</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.486987919035423</v>
+        <v>3.802308858547897</v>
       </c>
       <c r="C2" t="n">
-        <v>14.40714755982194</v>
+        <v>5.427101309076368</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7291608068149</v>
+        <v>22.47416844561798</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.44627859927157</v>
+        <v>18.11815388187489</v>
       </c>
       <c r="C3" t="n">
-        <v>30.39490892348125</v>
+        <v>32.85418692261951</v>
       </c>
       <c r="D3" t="n">
-        <v>68.38363633931158</v>
+        <v>78.22074833586463</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.54640116957152</v>
+        <v>36.36098972218912</v>
       </c>
       <c r="C4" t="n">
-        <v>122.3944862884499</v>
+        <v>138.7180053669616</v>
       </c>
       <c r="D4" t="n">
-        <v>97.57099558656925</v>
+        <v>127.0401164249458</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.65126824747669</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>191.6371518689774</v>
+        <v>212.8674459733147</v>
       </c>
       <c r="D5" t="n">
-        <v>71.15216486528759</v>
+        <v>88.16094384136359</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.99505987041232</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>191.758888584304</v>
+        <v>211.6432065861189</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>43.91455655866408</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.18285141936394</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>190.4394196697963</v>
+        <v>214.6934967032137</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>161.97364498516</v>
+        <v>186.5909686691488</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>96.07186684218435</v>
+        <v>106.4999909566939</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
         <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.285909566114074</v>
+        <v>2.334596040698915</v>
       </c>
       <c r="C2" t="n">
-        <v>6.861434704980958</v>
+        <v>2.725331626989146</v>
       </c>
       <c r="D2" t="n">
-        <v>10.27988021116835</v>
+        <v>15.82969998327557</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.22185928562655</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C3" t="n">
-        <v>43.17726403277472</v>
+        <v>30.32618658418397</v>
       </c>
       <c r="D3" t="n">
-        <v>67.39697989654353</v>
+        <v>79.87008447899926</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.40074265644449</v>
+        <v>39.43680527959437</v>
       </c>
       <c r="C4" t="n">
-        <v>117.8509579131956</v>
+        <v>133.7915953870511</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5687132959913</v>
+        <v>136.0123086940574</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.44295780772712</v>
+        <v>41.8469958935203</v>
       </c>
       <c r="C5" t="n">
-        <v>232.085157283946</v>
+        <v>257.7333160573939</v>
       </c>
       <c r="D5" t="n">
-        <v>75.69274799742909</v>
+        <v>90.76257525761763</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.18623863083319</v>
+        <v>31.87931145230244</v>
       </c>
       <c r="C6" t="n">
-        <v>229.4746901383538</v>
+        <v>246.3401339496097</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>43.27053006467818</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>202.8958345412798</v>
+        <v>229.1261697033461</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>118.413499347729</v>
+        <v>129.6790542539612</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
         <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>2.140209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.456733666653019</v>
+        <v>3.501894061048373</v>
       </c>
       <c r="C2" t="n">
-        <v>8.21526478913731</v>
+        <v>3.793473129209675</v>
       </c>
       <c r="D2" t="n">
-        <v>15.79141182280994</v>
+        <v>13.32526158974196</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99405276051229</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C3" t="n">
-        <v>34.99930565639879</v>
+        <v>20.84250376115979</v>
       </c>
       <c r="D3" t="n">
-        <v>61.33468782281948</v>
+        <v>75.3049576542516</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.95030038664446</v>
+        <v>36.73110860669016</v>
       </c>
       <c r="C4" t="n">
-        <v>113.9455655457018</v>
+        <v>106.734628658009</v>
       </c>
       <c r="D4" t="n">
-        <v>113.8689892247706</v>
+        <v>142.1894652491783</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.40769700583225</v>
+        <v>48.76831720846032</v>
       </c>
       <c r="C5" t="n">
-        <v>224.8938553503381</v>
+        <v>254.6408107890165</v>
       </c>
       <c r="D5" t="n">
-        <v>91.98975988792614</v>
+        <v>110.9374905798896</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.01393406097126</v>
+        <v>40.77492740048278</v>
       </c>
       <c r="C6" t="n">
-        <v>294.2798560956857</v>
+        <v>316.0157502677101</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>55.8692983532775</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>257.6920826538155</v>
+        <v>284.6410571353905</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>178.5799074024948</v>
+        <v>195.2696183746906</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>75.88124355664445</v>
+        <v>77.98905587766234</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3187,7 +3187,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.371902453460294</v>
+        <v>2.34245002233289</v>
       </c>
       <c r="C2" t="n">
-        <v>4.449280595646544</v>
+        <v>2.250165738133689</v>
       </c>
       <c r="D2" t="n">
-        <v>11.68476117594554</v>
+        <v>9.872454913905925</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.97656122828509</v>
+        <v>12.73817646260236</v>
       </c>
       <c r="C3" t="n">
-        <v>34.28753857081986</v>
+        <v>18.4224956701914</v>
       </c>
       <c r="D3" t="n">
-        <v>60.06823328434109</v>
+        <v>70.35204048632643</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.15977250054753</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>104.9478478362798</v>
+        <v>87.90961642907638</v>
       </c>
       <c r="D4" t="n">
-        <v>117.1872964651248</v>
+        <v>147.2817905911065</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.66004722355269</v>
+        <v>52.57258956241671</v>
       </c>
       <c r="C5" t="n">
-        <v>226.8573507588318</v>
+        <v>240.5527312330748</v>
       </c>
       <c r="D5" t="n">
-        <v>104.359780961436</v>
+        <v>124.2156282798277</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.09822549481625</v>
+        <v>46.08814597586652</v>
       </c>
       <c r="C6" t="n">
-        <v>328.2522536534423</v>
+        <v>357.7969690650459</v>
       </c>
       <c r="D6" t="n">
-        <v>59.89446394068941</v>
+        <v>66.49573550404497</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>14.9117658798048</v>
       </c>
       <c r="C7" t="n">
-        <v>315.8419809240584</v>
+        <v>344.0485742147735</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>222.3069501496477</v>
+        <v>242.0842576516997</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>82.64843048201772</v>
+        <v>82.09374302911826</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.30999559483051</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.029673415305656</v>
+        <v>3.544109212330985</v>
       </c>
       <c r="C2" t="n">
-        <v>8.406705591465437</v>
+        <v>6.46088164164826</v>
       </c>
       <c r="D2" t="n">
-        <v>17.91984084561703</v>
+        <v>17.15015064548753</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.74170254279185</v>
+        <v>10.45561305022853</v>
       </c>
       <c r="C3" t="n">
-        <v>26.74280746368311</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="D3" t="n">
-        <v>56.60266388834986</v>
+        <v>63.60743375815085</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.12300586713388</v>
+        <v>28.69059490890879</v>
       </c>
       <c r="C4" t="n">
-        <v>96.38406261213485</v>
+        <v>70.32258805519903</v>
       </c>
       <c r="D4" t="n">
-        <v>117.7360934317987</v>
+        <v>147.5880958748315</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.09554229361077</v>
+        <v>51.71356032120075</v>
       </c>
       <c r="C5" t="n">
-        <v>212.5238342768283</v>
+        <v>208.7686493080843</v>
       </c>
       <c r="D5" t="n">
-        <v>117.4415691205247</v>
+        <v>140.267203244263</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.96617258082844</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>341.5755517477758</v>
+        <v>368.0208896570721</v>
       </c>
       <c r="D6" t="n">
-        <v>72.97625209977816</v>
+        <v>80.7850733393573</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="C7" t="n">
-        <v>376.5670034225406</v>
+        <v>408.4865665307171</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>294.7402957689774</v>
+        <v>321.1100391050467</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>150.0984247545905</v>
+        <v>152.5390495473481</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>54.23665192111504</v>
+        <v>51.81664383014665</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.684720118216532</v>
+        <v>7.796058519423921</v>
       </c>
       <c r="C2" t="n">
-        <v>12.29540824798705</v>
+        <v>19.13622625117883</v>
       </c>
       <c r="D2" t="n">
-        <v>4.935245709248716</v>
+        <v>3.049308369390593</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.217768063893545</v>
+        <v>2.615375884113503</v>
       </c>
       <c r="C2" t="n">
-        <v>4.976479112827081</v>
+        <v>3.876921684070654</v>
       </c>
       <c r="D2" t="n">
-        <v>13.33213382367168</v>
+        <v>12.75879316439155</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58033606639688</v>
+        <v>13.79846398318892</v>
       </c>
       <c r="C3" t="n">
-        <v>32.71674224402496</v>
+        <v>19.58586669972387</v>
       </c>
       <c r="D3" t="n">
-        <v>62.83185307179587</v>
+        <v>70.22441328477434</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.78362426110075</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="C4" t="n">
-        <v>134.0723752304657</v>
+        <v>106.1347808107142</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6294838426633</v>
+        <v>148.5452998864722</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.15915060574178</v>
+        <v>30.31146036862028</v>
       </c>
       <c r="C5" t="n">
-        <v>299.9730110326129</v>
+        <v>310.796779471934</v>
       </c>
       <c r="D5" t="n">
-        <v>106.7896065294468</v>
+        <v>124.26471566504</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>16.78494049950772</v>
       </c>
       <c r="C6" t="n">
-        <v>308.2874323398792</v>
+        <v>330.3453397588966</v>
       </c>
       <c r="D6" t="n">
-        <v>60.73974871404592</v>
+        <v>65.32843748369551</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>207.2675570682908</v>
+        <v>225.832406155598</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>110.569335190797</v>
+        <v>112.4052033977386</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>23.699389580518</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>39.49374664644068</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>19.30312336090078</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>20.21418523044183</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.81497376771187</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.252170291271189</v>
+        <v>7.831401436776806</v>
       </c>
       <c r="C2" t="n">
-        <v>7.35034506169587</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D2" t="n">
-        <v>9.013425672689966</v>
+        <v>17.50161632360789</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.19607180340888</v>
+        <v>16.55226629360122</v>
       </c>
       <c r="C3" t="n">
-        <v>30.98395754602934</v>
+        <v>48.21853849408209</v>
       </c>
       <c r="D3" t="n">
-        <v>7.279659226990098</v>
+        <v>5.699045423152734</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39789630410582</v>
+        <v>13.39685661208867</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14192770973047</v>
+        <v>70.13648461622894</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576223094600685</v>
+        <v>1.576100777892785</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.556692006036947</v>
+        <v>5.491896657556658</v>
       </c>
       <c r="C2" t="n">
-        <v>7.713591712267189</v>
+        <v>5.138467484027806</v>
       </c>
       <c r="D2" t="n">
-        <v>11.52964503867454</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.71978529812893</v>
+        <v>22.71273313774996</v>
       </c>
       <c r="C3" t="n">
-        <v>29.53097094374406</v>
+        <v>47.76202581160732</v>
       </c>
       <c r="D3" t="n">
-        <v>13.09160563613122</v>
+        <v>18.37340828497906</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.46390900021901</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="C4" t="n">
-        <v>47.75809882079034</v>
+        <v>72.79855576530949</v>
       </c>
       <c r="D4" t="n">
-        <v>18.88882582970863</v>
+        <v>17.91885909791278</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.50317890838889</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43965154173065</v>
+        <v>15.43250302523808</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13700333807628</v>
+        <v>86.09712214080193</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250452956153822</v>
+        <v>3.24894800531328</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.864559874542945</v>
+        <v>4.94015444776995</v>
       </c>
       <c r="C2" t="n">
-        <v>5.655848524165874</v>
+        <v>3.6471927212769</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33191283949343</v>
+        <v>18.37929877120454</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89020848804038</v>
+        <v>20.60688431214055</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11020208924968</v>
+        <v>31.43065275146164</v>
       </c>
       <c r="D3" t="n">
-        <v>19.27661617288612</v>
+        <v>26.12921514852886</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9158160438088</v>
+        <v>32.77466535857552</v>
       </c>
       <c r="C4" t="n">
-        <v>62.46075243959057</v>
+        <v>98.69411496022759</v>
       </c>
       <c r="D4" t="n">
-        <v>21.21164089795658</v>
+        <v>22.64106555533994</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.18625432636641</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>52.57258956241671</v>
+        <v>77.68078709852888</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>29.42788743479815</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.997496725243765</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5364,7 +5364,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72998859618955</v>
+        <v>16.71211416129419</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0529304367563</v>
+        <v>101.1082906758299</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182497149047388</v>
+        <v>4.178028540323548</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.917975161199774</v>
+        <v>5.993569734426777</v>
       </c>
       <c r="C2" t="n">
-        <v>8.583420178229863</v>
+        <v>9.590693322787089</v>
       </c>
       <c r="D2" t="n">
-        <v>18.8986433067511</v>
+        <v>27.72553691563417</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09851892778995</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="C3" t="n">
-        <v>25.38308689330128</v>
+        <v>21.75552912610932</v>
       </c>
       <c r="D3" t="n">
-        <v>22.84036033930204</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>36.16954891986099</v>
       </c>
       <c r="C4" t="n">
-        <v>69.65892660712818</v>
+        <v>87.83304010814514</v>
       </c>
       <c r="D4" t="n">
-        <v>25.83174559414208</v>
+        <v>29.55845987946297</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.52606220522283</v>
+        <v>32.0295188510522</v>
       </c>
       <c r="C5" t="n">
-        <v>86.49197274414401</v>
+        <v>131.2842117504048</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23782929080177</v>
+        <v>30.9495963763807</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.39751000922872</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>48.90576188705487</v>
+        <v>68.58882160949918</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.53898915629405</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05112081675686</v>
+        <v>18.01588132358001</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7620738997947</v>
+        <v>115.8163799373001</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017040272252286</v>
+        <v>6.005293774526671</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.699847244407733</v>
+        <v>6.139850142359552</v>
       </c>
       <c r="C2" t="n">
-        <v>7.522150909939061</v>
+        <v>8.95059381961817</v>
       </c>
       <c r="D2" t="n">
-        <v>20.31137825316226</v>
+        <v>32.45559735469531</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20021977840412</v>
+        <v>17.28857707178633</v>
       </c>
       <c r="C3" t="n">
-        <v>28.0092620021615</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D3" t="n">
-        <v>30.21819433671682</v>
+        <v>43.74667770123787</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.28294862746811</v>
+        <v>25.78069471352124</v>
       </c>
       <c r="C4" t="n">
-        <v>54.82864578677587</v>
+        <v>57.67473238138736</v>
       </c>
       <c r="D4" t="n">
-        <v>27.15906849028376</v>
+        <v>33.5021404074224</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.66641106920112</v>
+        <v>26.26175108860219</v>
       </c>
       <c r="C5" t="n">
-        <v>81.06781667818038</v>
+        <v>109.1703447122453</v>
       </c>
       <c r="D5" t="n">
-        <v>26.23720739599601</v>
+        <v>27.93072218582176</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.28933783531233</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>63.51711296936016</v>
+        <v>92.498305198726</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>29.58398531977338</v>
+        <v>37.60879105428681</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052258303694666</v>
+        <v>7.030817284419134</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1149215971375</v>
+        <v>65.035059880877</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407661439809167</v>
+        <v>4.394260802761959</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39863062565321</v>
+        <v>5.759913780816037</v>
       </c>
       <c r="C2" t="n">
-        <v>4.325580384911446</v>
+        <v>10.47622975201771</v>
       </c>
       <c r="D2" t="n">
-        <v>17.65476896547039</v>
+        <v>27.53605960871454</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04652735719387</v>
+        <v>19.89020848804038</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9026524130261</v>
+        <v>32.39767424014475</v>
       </c>
       <c r="D3" t="n">
-        <v>39.97676651693012</v>
+        <v>60.85854018625978</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.36251124924111</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="C4" t="n">
-        <v>64.56660126519998</v>
+        <v>65.6386697582375</v>
       </c>
       <c r="D4" t="n">
-        <v>36.42480332296516</v>
+        <v>47.56665801846221</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.74128593663113</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>93.63418729253955</v>
+        <v>107.8695290041183</v>
       </c>
       <c r="D5" t="n">
-        <v>30.65507206510666</v>
+        <v>34.06664533736433</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.27803988894688</v>
+        <v>26.12332466230338</v>
       </c>
       <c r="C6" t="n">
-        <v>102.0379476408923</v>
+        <v>138.747457798089</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>12.51630148144259</v>
       </c>
       <c r="C7" t="n">
-        <v>65.81538434500192</v>
+        <v>91.44685340747763</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>30.62561963397925</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272564553739705</v>
+        <v>7.241664257226403</v>
       </c>
       <c r="C21" t="n">
-        <v>75.45285724504944</v>
+        <v>74.22705863657062</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454423415304778</v>
+        <v>5.431248192919802</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.280240064066846</v>
+        <v>5.640140560897926</v>
       </c>
       <c r="C2" t="n">
-        <v>13.33017032826319</v>
+        <v>12.53397294011903</v>
       </c>
       <c r="D2" t="n">
-        <v>15.63825918094744</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59215809657685</v>
+        <v>19.74785507092459</v>
       </c>
       <c r="C3" t="n">
-        <v>21.68680678681204</v>
+        <v>37.1493331286993</v>
       </c>
       <c r="D3" t="n">
-        <v>44.82169143738813</v>
+        <v>68.24619166071703</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.7220929509027</v>
+        <v>34.48486985937346</v>
       </c>
       <c r="C4" t="n">
-        <v>68.484756352849</v>
+        <v>74.26626858315846</v>
       </c>
       <c r="D4" t="n">
-        <v>48.26860762699868</v>
+        <v>66.30233120630834</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.71169463678348</v>
+        <v>40.0307626406637</v>
       </c>
       <c r="C5" t="n">
-        <v>108.3849465488479</v>
+        <v>115.1344620155447</v>
       </c>
       <c r="D5" t="n">
-        <v>36.59464567579986</v>
+        <v>42.60785036431157</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.86422538384024</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="C6" t="n">
-        <v>128.0405173355733</v>
+        <v>154.9286234594849</v>
       </c>
       <c r="D6" t="n">
-        <v>35.22019888985433</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>110.4309087644982</v>
+        <v>148.8781123582118</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>60.8339964936536</v>
+        <v>79.77681844709581</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.479818331660765</v>
+        <v>7.437225302760749</v>
       </c>
       <c r="C21" t="n">
-        <v>84.14795623118361</v>
+        <v>82.73913149321334</v>
       </c>
       <c r="D21" t="n">
-        <v>6.54484104020317</v>
+        <v>6.507572139915656</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497624874427</v>
+        <v>10.84497626835271</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907165105743</v>
+        <v>37.78907171938261</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.083890523217484</v>
+        <v>5.883613991551134</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14029211071606</v>
+        <v>10.04622425755761</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64226828722244</v>
+        <v>37.88073516836317</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.23243752619501</v>
+        <v>16.06139244147782</v>
       </c>
       <c r="C3" t="n">
-        <v>42.89746593706438</v>
+        <v>25.68251994309656</v>
       </c>
       <c r="D3" t="n">
-        <v>77.6856958370501</v>
+        <v>105.4642471287136</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.69732827411827</v>
+        <v>34.94432778496097</v>
       </c>
       <c r="C4" t="n">
-        <v>82.71518932590652</v>
+        <v>60.98027690158638</v>
       </c>
       <c r="D4" t="n">
-        <v>81.7835107545763</v>
+        <v>123.874961826454</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.7248993252952</v>
+        <v>47.1238898038469</v>
       </c>
       <c r="C5" t="n">
-        <v>125.7618809140164</v>
+        <v>70.24404823885929</v>
       </c>
       <c r="D5" t="n">
-        <v>55.14967728606459</v>
+        <v>75.69274799742909</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.1560664939088</v>
+        <v>45.12210623488766</v>
       </c>
       <c r="C6" t="n">
-        <v>167.1651268452172</v>
+        <v>71.52719248830986</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01014593887452</v>
+        <v>46.81267578160067</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.56024344842221</v>
       </c>
       <c r="C7" t="n">
-        <v>185.5886042631128</v>
+        <v>67.13288976410114</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>15.93867397844697</v>
       </c>
       <c r="C8" t="n">
-        <v>133.9349305518711</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>64.34374453633593</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.615512221103435</v>
+        <v>7.710689521330387</v>
       </c>
       <c r="C21" t="n">
-        <v>91.38614665324121</v>
+        <v>96.38361901662985</v>
       </c>
       <c r="D21" t="n">
-        <v>7.615512221103435</v>
+        <v>8.674525711496686</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.167339078078462</v>
+        <v>8.525497063679301</v>
       </c>
       <c r="C2" t="n">
-        <v>12.90605532002857</v>
+        <v>6.367615609744812</v>
       </c>
       <c r="D2" t="n">
-        <v>27.93563092434299</v>
+        <v>39.45251324286232</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.40424337443821</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="C3" t="n">
-        <v>44.57134577280519</v>
+        <v>32.57438882690916</v>
       </c>
       <c r="D3" t="n">
-        <v>79.0552338844744</v>
+        <v>109.7888457659208</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.33997210977243</v>
+        <v>32.86400439966198</v>
       </c>
       <c r="C4" t="n">
-        <v>93.71665409969629</v>
+        <v>61.96300635353744</v>
       </c>
       <c r="D4" t="n">
-        <v>97.74967366874218</v>
+        <v>143.4529745445439</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.67014243803564</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="C5" t="n">
-        <v>135.9966007307894</v>
+        <v>91.35162388016572</v>
       </c>
       <c r="D5" t="n">
-        <v>67.64241682260524</v>
+        <v>99.89282890711299</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.84413276586557</v>
+        <v>53.97747052719389</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1261600366836</v>
+        <v>90.2039608139012</v>
       </c>
       <c r="D6" t="n">
-        <v>46.73217246985243</v>
+        <v>57.60011955586462</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.06414206260808</v>
+        <v>42.51949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>211.4596197654247</v>
+        <v>85.15875936177682</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.53249247079604</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="C8" t="n">
-        <v>181.4171582677681</v>
+        <v>67.09263810822702</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>107.7203033530728</v>
+        <v>45.48437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>50.82016991033614</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.777038338815971</v>
+        <v>7.896760132264616</v>
       </c>
       <c r="C21" t="n">
-        <v>99.15723881990363</v>
+        <v>105.6191667690392</v>
       </c>
       <c r="D21" t="n">
-        <v>8.749168131167966</v>
+        <v>9.87095016533077</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.503096792930871</v>
+        <v>10.42714236680537</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32838675930394</v>
+        <v>7.591854996940584</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64619527803943</v>
+        <v>35.70616400345649</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29625112697106</v>
+        <v>22.60964962880404</v>
       </c>
       <c r="C3" t="n">
-        <v>46.40721397974673</v>
+        <v>28.54431450097601</v>
       </c>
       <c r="D3" t="n">
-        <v>80.91073704550088</v>
+        <v>113.7796501836841</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.77841242294325</v>
+        <v>32.83847895935156</v>
       </c>
       <c r="C4" t="n">
-        <v>99.58750537109221</v>
+        <v>70.92243590249383</v>
       </c>
       <c r="D4" t="n">
-        <v>108.3172059572548</v>
+        <v>160.899612996714</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.67643383488862</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>148.8329519638165</v>
+        <v>100.5800523000858</v>
       </c>
       <c r="D5" t="n">
-        <v>81.75504007115315</v>
+        <v>121.2212977818749</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.63407981488576</v>
+        <v>60.21647718768238</v>
       </c>
       <c r="C6" t="n">
-        <v>194.6972594631147</v>
+        <v>113.6304245326386</v>
       </c>
       <c r="D6" t="n">
-        <v>53.65545728020094</v>
+        <v>72.13096732642167</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.9691745772034</v>
+        <v>51.86180422454201</v>
       </c>
       <c r="C7" t="n">
-        <v>229.7849224128957</v>
+        <v>105.7597531876919</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.87596529856218</v>
+        <v>33.71321616383547</v>
       </c>
       <c r="C8" t="n">
-        <v>219.4696992843744</v>
+        <v>87.12029127486194</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>40.88979188187965</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.75312366234431</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C9" t="n">
-        <v>152.3171745661883</v>
+        <v>62.56874468705769</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>79.8602670019568</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>42.11403126907541</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.921314811852151</v>
+        <v>8.067232489034337</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9475856085225</v>
+        <v>113.94965890761</v>
       </c>
       <c r="D21" t="n">
-        <v>8.911479163333668</v>
+        <v>11.09244467242221</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.162430339557228</v>
+        <v>9.27653405742811</v>
       </c>
       <c r="C2" t="n">
-        <v>8.1563599268825</v>
+        <v>5.101161071266427</v>
       </c>
       <c r="D2" t="n">
-        <v>21.44824209468007</v>
+        <v>29.15299807760903</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.06616231127881</v>
+        <v>25.39781310886498</v>
       </c>
       <c r="C3" t="n">
-        <v>66.36123606856314</v>
+        <v>42.99564070748906</v>
       </c>
       <c r="D3" t="n">
-        <v>86.20726590991242</v>
+        <v>124.7015933934299</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.86628669023996</v>
+        <v>23.68760860806704</v>
       </c>
       <c r="C4" t="n">
-        <v>124.9597930396468</v>
+        <v>90.37282141903162</v>
       </c>
       <c r="D4" t="n">
-        <v>99.45987816954012</v>
+        <v>149.5407920585784</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.90680038802134</v>
+        <v>33.91938318172731</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3371029532471</v>
+        <v>67.88785374866696</v>
       </c>
       <c r="D5" t="n">
-        <v>53.23526926278331</v>
+        <v>76.84630154991909</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.78622534684823</v>
+        <v>32.20132469929539</v>
       </c>
       <c r="C6" t="n">
-        <v>151.3462260866883</v>
+        <v>69.63536466222628</v>
       </c>
       <c r="D6" t="n">
-        <v>28.2566624236317</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3277938644858</v>
+        <v>61.26400198811371</v>
       </c>
       <c r="D7" t="n">
-        <v>27.008861091534</v>
+        <v>28.7455727803466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>112.2383062880166</v>
+        <v>46.06360228326034</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.052474596681584</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.838633523605029</v>
+        <v>5.39568538254047</v>
       </c>
       <c r="C2" t="n">
-        <v>3.931899555508476</v>
+        <v>2.717477645355171</v>
       </c>
       <c r="D2" t="n">
-        <v>15.25046883776995</v>
+        <v>19.79988769924967</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.67837196810132</v>
+        <v>29.27571654063988</v>
       </c>
       <c r="C3" t="n">
-        <v>50.69745144730529</v>
+        <v>31.6564547234384</v>
       </c>
       <c r="D3" t="n">
-        <v>84.89663272474293</v>
+        <v>120.3819034947439</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>34.62525978108076</v>
       </c>
       <c r="C4" t="n">
-        <v>147.7029603562284</v>
+        <v>101.1573199501829</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1370063480299</v>
+        <v>174.6961134844944</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>37.03643214271093</v>
       </c>
       <c r="C5" t="n">
-        <v>164.7863521578271</v>
+        <v>114.4472386225719</v>
       </c>
       <c r="D5" t="n">
-        <v>68.52598975642738</v>
+        <v>102.2735670899115</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.61642405174254</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="C6" t="n">
-        <v>173.1626235704609</v>
+        <v>88.67439789068467</v>
       </c>
       <c r="D6" t="n">
-        <v>33.81139093426016</v>
+        <v>41.13719230334986</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>183.0134800348734</v>
+        <v>77.61304650693583</v>
       </c>
       <c r="D7" t="n">
-        <v>29.40432548989622</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>143.9487571351885</v>
+        <v>60.0829594999048</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850594422505238</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.802308858547897</v>
+        <v>5.673519982842318</v>
       </c>
       <c r="C2" t="n">
-        <v>5.427101309076368</v>
+        <v>7.937430188835462</v>
       </c>
       <c r="D2" t="n">
-        <v>22.47416844561798</v>
+        <v>20.79832511446867</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11815388187489</v>
+        <v>23.74356822720911</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85418692261951</v>
+        <v>20.34672117051515</v>
       </c>
       <c r="D3" t="n">
-        <v>78.22074833586463</v>
+        <v>110.1717273705771</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.36098972218912</v>
+        <v>45.23108023005904</v>
       </c>
       <c r="C4" t="n">
-        <v>138.7180053669616</v>
+        <v>89.63258365002955</v>
       </c>
       <c r="D4" t="n">
-        <v>127.0401164249458</v>
+        <v>190.2666320738488</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>44.00684084286328</v>
       </c>
       <c r="C5" t="n">
-        <v>212.8674459733147</v>
+        <v>151.6063892283137</v>
       </c>
       <c r="D5" t="n">
-        <v>88.16094384136359</v>
+        <v>137.2974164389165</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>43.99505987041232</v>
       </c>
       <c r="C6" t="n">
-        <v>211.6432065861189</v>
+        <v>132.4681994817264</v>
       </c>
       <c r="D6" t="n">
-        <v>43.91455655866408</v>
+        <v>60.01521890831177</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>31.14103717870882</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6934967032137</v>
+        <v>102.2863298100667</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>186.5909686691488</v>
+        <v>80.36095833112266</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>106.4999909566939</v>
+        <v>54.47030787472577</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>38.00836236991527</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>22.99842171968578</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.334596040698915</v>
+        <v>3.325179474283947</v>
       </c>
       <c r="C2" t="n">
-        <v>2.725331626989146</v>
+        <v>3.655046702910875</v>
       </c>
       <c r="D2" t="n">
-        <v>15.82969998327557</v>
+        <v>14.3433339590459</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84326452468578</v>
+        <v>24.20498964820511</v>
       </c>
       <c r="C3" t="n">
-        <v>30.32618658418397</v>
+        <v>26.34519964346316</v>
       </c>
       <c r="D3" t="n">
-        <v>79.87008447899926</v>
+        <v>106.8337851761379</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>50.11920204950392</v>
       </c>
       <c r="C4" t="n">
-        <v>133.7915953870511</v>
+        <v>84.02974950189299</v>
       </c>
       <c r="D4" t="n">
-        <v>136.0123086940574</v>
+        <v>203.5270983151105</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.8469958935203</v>
+        <v>46.14214209960009</v>
       </c>
       <c r="C5" t="n">
-        <v>257.7333160573939</v>
+        <v>178.8253443285565</v>
       </c>
       <c r="D5" t="n">
-        <v>90.76257525761763</v>
+        <v>148.4647965747239</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>37.59504658642736</v>
       </c>
       <c r="C6" t="n">
-        <v>246.3401339496097</v>
+        <v>159.1952989821416</v>
       </c>
       <c r="D6" t="n">
-        <v>43.27053006467818</v>
+        <v>57.9623844587317</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>229.1261697033461</v>
+        <v>106.5382791171596</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>129.6790542539612</v>
+        <v>65.34021845614646</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.30272245027328</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.501894061048373</v>
+        <v>3.93680829402971</v>
       </c>
       <c r="C2" t="n">
-        <v>3.793473129209675</v>
+        <v>5.068763397026282</v>
       </c>
       <c r="D2" t="n">
-        <v>13.32526158974196</v>
+        <v>17.1913840490659</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.27813769993811</v>
+        <v>17.82362957060084</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84250376115979</v>
+        <v>20.10128424445344</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3049576542516</v>
+        <v>94.87609813841175</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.73110860669016</v>
+        <v>48.76635371305181</v>
       </c>
       <c r="C4" t="n">
-        <v>106.734628658009</v>
+        <v>75.63187963976578</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1894652491783</v>
+        <v>209.4490004671273</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.76831720846032</v>
+        <v>58.53670686571608</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6408107890165</v>
+        <v>169.0324109786946</v>
       </c>
       <c r="D5" t="n">
-        <v>110.9374905798896</v>
+        <v>182.6787040677253</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.77492740048278</v>
+        <v>47.69821221083129</v>
       </c>
       <c r="C6" t="n">
-        <v>316.0157502677101</v>
+        <v>215.9098821087756</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8692983532775</v>
+        <v>82.11337798320324</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="C7" t="n">
-        <v>284.6410571353905</v>
+        <v>160.915320959982</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>42.10028680121597</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>195.2696183746906</v>
+        <v>96.71687508387453</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>77.98905587766234</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34245002233289</v>
+        <v>2.746930076482576</v>
       </c>
       <c r="C2" t="n">
-        <v>2.250165738133689</v>
+        <v>2.807798434145878</v>
       </c>
       <c r="D2" t="n">
-        <v>9.872454913905925</v>
+        <v>14.6516027381794</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.73817646260236</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4224956701914</v>
+        <v>20.12091919853838</v>
       </c>
       <c r="D3" t="n">
-        <v>70.35204048632643</v>
+        <v>88.6420002164445</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.96610616090365</v>
+        <v>44.22282533779757</v>
       </c>
       <c r="C4" t="n">
-        <v>87.90961642907638</v>
+        <v>66.58311104972293</v>
       </c>
       <c r="D4" t="n">
-        <v>147.2817905911065</v>
+        <v>210.0871364748877</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.57258956241671</v>
+        <v>65.43348448804993</v>
       </c>
       <c r="C5" t="n">
-        <v>240.5527312330748</v>
+        <v>163.3873616792754</v>
       </c>
       <c r="D5" t="n">
-        <v>124.2156282798277</v>
+        <v>205.9706683509809</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.08814597586652</v>
+        <v>56.19131160027045</v>
       </c>
       <c r="C6" t="n">
-        <v>357.7969690650459</v>
+        <v>243.8445312854143</v>
       </c>
       <c r="D6" t="n">
-        <v>66.49573550404497</v>
+        <v>101.5146761145287</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.9117658798048</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>344.0485742147735</v>
+        <v>211.1601867156295</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>48.68781389671206</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>242.0842576516997</v>
+        <v>126.591457724105</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>82.09374302911826</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.544109212330985</v>
+        <v>3.895574890451343</v>
       </c>
       <c r="C2" t="n">
-        <v>6.46088164164826</v>
+        <v>8.501935118777377</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15015064548753</v>
+        <v>27.25724326070844</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.45561305022853</v>
+        <v>12.86580366415445</v>
       </c>
       <c r="C3" t="n">
-        <v>14.12244072559037</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D3" t="n">
-        <v>63.60743375815085</v>
+        <v>81.12181280191395</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.69059490890879</v>
+        <v>37.73936349895164</v>
       </c>
       <c r="C4" t="n">
-        <v>70.32258805519903</v>
+        <v>58.52983463178634</v>
       </c>
       <c r="D4" t="n">
-        <v>147.5880958748315</v>
+        <v>206.6284393128262</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.71356032120075</v>
+        <v>66.34160111447822</v>
       </c>
       <c r="C5" t="n">
-        <v>208.7686493080843</v>
+        <v>145.3968349989526</v>
       </c>
       <c r="D5" t="n">
-        <v>140.267203244263</v>
+        <v>226.317389521496</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>67.58253021264619</v>
       </c>
       <c r="C6" t="n">
-        <v>368.0208896570721</v>
+        <v>253.6256836628253</v>
       </c>
       <c r="D6" t="n">
-        <v>80.7850733393573</v>
+        <v>128.6845438295592</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.06874770149305</v>
+        <v>35.87207936547421</v>
       </c>
       <c r="C7" t="n">
-        <v>408.4865665307171</v>
+        <v>267.5134866871006</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>61.20411537815465</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>321.1100391050467</v>
+        <v>185.673034565678</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>152.5390495473481</v>
+        <v>94.2968669929061</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.796058519423921</v>
+        <v>4.966661635784614</v>
       </c>
       <c r="C2" t="n">
-        <v>19.13622625117883</v>
+        <v>3.821943812632833</v>
       </c>
       <c r="D2" t="n">
-        <v>3.049308369390593</v>
+        <v>6.62679700366597</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.615375884113503</v>
+        <v>2.790126975469435</v>
       </c>
       <c r="C2" t="n">
-        <v>3.876921684070654</v>
+        <v>4.828235209485814</v>
       </c>
       <c r="D2" t="n">
-        <v>12.75879316439155</v>
+        <v>20.06201433628357</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.79846398318892</v>
+        <v>17.24930716361646</v>
       </c>
       <c r="C3" t="n">
-        <v>19.58586669972387</v>
+        <v>23.41959148480766</v>
       </c>
       <c r="D3" t="n">
-        <v>70.22441328477434</v>
+        <v>91.93576376419256</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>51.16574510223102</v>
       </c>
       <c r="C4" t="n">
-        <v>106.1347808107142</v>
+        <v>83.76173237863361</v>
       </c>
       <c r="D4" t="n">
-        <v>148.5452998864722</v>
+        <v>212.7162568268606</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.31146036862028</v>
+        <v>39.90804417763285</v>
       </c>
       <c r="C5" t="n">
-        <v>310.796779471934</v>
+        <v>216.1563007825415</v>
       </c>
       <c r="D5" t="n">
-        <v>124.26471566504</v>
+        <v>201.380997833627</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.78494049950772</v>
+        <v>22.25916569838794</v>
       </c>
       <c r="C6" t="n">
-        <v>330.3453397588966</v>
+        <v>225.8922927655571</v>
       </c>
       <c r="D6" t="n">
-        <v>65.32843748369551</v>
+        <v>98.09328536522857</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>225.832406155598</v>
+        <v>130.5528097107408</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>112.4052033977386</v>
+        <v>69.5126461991954</v>
       </c>
       <c r="D8" t="n">
-        <v>23.699389580518</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>19.30312336090078</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.21418523044183</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.21570675749381</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.831401436776806</v>
+        <v>7.428884878035614</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98615772114931</v>
+        <v>2.894192232119597</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50161632360789</v>
+        <v>9.508226515630358</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.55226629360122</v>
+        <v>10.55378782065321</v>
       </c>
       <c r="C3" t="n">
-        <v>48.21853849408209</v>
+        <v>9.783115872819465</v>
       </c>
       <c r="D3" t="n">
-        <v>5.699045423152734</v>
+        <v>8.968265278294613</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39685661208867</v>
+        <v>13.39935767769673</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13648461622894</v>
+        <v>70.14957843029467</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576100777892785</v>
+        <v>1.576395020905498</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.491896657556658</v>
+        <v>5.542947538177491</v>
       </c>
       <c r="C2" t="n">
-        <v>5.138467484027806</v>
+        <v>4.645630136495907</v>
       </c>
       <c r="D2" t="n">
-        <v>15.58328130950962</v>
+        <v>24.23444207933251</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.71273313774996</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="C3" t="n">
-        <v>47.76202581160732</v>
+        <v>10.74522862298134</v>
       </c>
       <c r="D3" t="n">
-        <v>18.37340828497906</v>
+        <v>14.78512042595696</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.76119862815655</v>
+        <v>12.34155039008665</v>
       </c>
       <c r="C4" t="n">
-        <v>72.79855576530949</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="D4" t="n">
-        <v>17.91885909791278</v>
+        <v>19.76945352041802</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.53525778745954</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43250302523808</v>
+        <v>15.44641566966819</v>
       </c>
       <c r="C21" t="n">
-        <v>86.09712214080193</v>
+        <v>86.17474005183308</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24894800531328</v>
+        <v>3.251876983088041</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.94015444776995</v>
+        <v>5.730461349688632</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6471927212769</v>
+        <v>3.763038950378024</v>
       </c>
       <c r="D2" t="n">
-        <v>18.37929877120454</v>
+        <v>35.61289797155305</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.60688431214055</v>
+        <v>19.71349390127595</v>
       </c>
       <c r="C3" t="n">
-        <v>31.43065275146164</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="D3" t="n">
-        <v>26.12921514852886</v>
+        <v>30.73852061996763</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.77466535857552</v>
+        <v>27.01867856857647</v>
       </c>
       <c r="C4" t="n">
-        <v>98.69411496022759</v>
+        <v>22.14331946928681</v>
       </c>
       <c r="D4" t="n">
-        <v>22.64106555533994</v>
+        <v>22.55172651425348</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.70796326794897</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C5" t="n">
-        <v>77.68078709852888</v>
+        <v>19.07044915499429</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.43776166510284</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71211416129419</v>
+        <v>16.74562430274197</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1082906758299</v>
+        <v>102.148308246726</v>
       </c>
       <c r="D21" t="n">
-        <v>4.178028540323548</v>
+        <v>5.023687290822592</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.993569734426777</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="C2" t="n">
-        <v>9.590693322787089</v>
+        <v>3.301617529382023</v>
       </c>
       <c r="D2" t="n">
-        <v>27.72553691563417</v>
+        <v>38.50807195137689</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54521413322225</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="C3" t="n">
-        <v>21.75552912610932</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="D3" t="n">
-        <v>33.80157345721769</v>
+        <v>50.96743206597316</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>32.95334344074844</v>
       </c>
       <c r="C4" t="n">
-        <v>87.83304010814514</v>
+        <v>31.17932533917445</v>
       </c>
       <c r="D4" t="n">
-        <v>29.55845987946297</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.0295188510522</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C5" t="n">
-        <v>131.2842117504048</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="D5" t="n">
-        <v>30.9495963763807</v>
+        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.24279478258523</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>68.58882160949918</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="D6" t="n">
-        <v>37.23278168356029</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>49.53898915629405</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.01588132358001</v>
+        <v>18.07859585980969</v>
       </c>
       <c r="C21" t="n">
-        <v>115.8163799373001</v>
+        <v>117.9413158473299</v>
       </c>
       <c r="D21" t="n">
-        <v>6.005293774526671</v>
+        <v>6.887084137070359</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.139850142359552</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="C2" t="n">
-        <v>8.95059381961817</v>
+        <v>7.011642103730719</v>
       </c>
       <c r="D2" t="n">
-        <v>32.45559735469531</v>
+        <v>44.9218297032213</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.28857707178633</v>
+        <v>16.44427404613408</v>
       </c>
       <c r="C3" t="n">
-        <v>28.20561154301086</v>
+        <v>12.86089492563322</v>
       </c>
       <c r="D3" t="n">
-        <v>43.74667770123787</v>
+        <v>64.81007469585319</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.78069471352124</v>
+        <v>26.26567807941916</v>
       </c>
       <c r="C4" t="n">
-        <v>57.67473238138736</v>
+        <v>28.98413747247858</v>
       </c>
       <c r="D4" t="n">
-        <v>33.5021404074224</v>
+        <v>42.93379060212151</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.26175108860219</v>
+        <v>23.21833320543707</v>
       </c>
       <c r="C5" t="n">
-        <v>109.1703447122453</v>
+        <v>33.67394625566561</v>
       </c>
       <c r="D5" t="n">
-        <v>27.93072218582176</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93336432929824</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>92.498305198726</v>
+        <v>24.71451670670921</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>37.60879105428681</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.030817284419134</v>
+        <v>7.069037042585524</v>
       </c>
       <c r="C21" t="n">
-        <v>65.035059880877</v>
+        <v>67.15585190456247</v>
       </c>
       <c r="D21" t="n">
-        <v>4.394260802761959</v>
+        <v>5.301777781939143</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.759913780816037</v>
+        <v>4.842961425049515</v>
       </c>
       <c r="C2" t="n">
-        <v>10.47622975201771</v>
+        <v>8.533351045313276</v>
       </c>
       <c r="D2" t="n">
-        <v>27.53605960871454</v>
+        <v>42.22595050735956</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89020848804038</v>
+        <v>19.69876768571225</v>
       </c>
       <c r="C3" t="n">
-        <v>32.39767424014475</v>
+        <v>22.39366513386975</v>
       </c>
       <c r="D3" t="n">
-        <v>60.85854018625978</v>
+        <v>88.05786033241766</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.3497485290859</v>
+        <v>30.40079940970673</v>
       </c>
       <c r="C4" t="n">
-        <v>65.6386697582375</v>
+        <v>31.11551173839841</v>
       </c>
       <c r="D4" t="n">
-        <v>47.56665801846221</v>
+        <v>68.14016290865837</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>33.08489763311751</v>
       </c>
       <c r="C5" t="n">
-        <v>107.8695290041183</v>
+        <v>46.09305471438775</v>
       </c>
       <c r="D5" t="n">
-        <v>34.06664533736433</v>
+        <v>39.04901493641689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.12332466230338</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="C6" t="n">
-        <v>138.747457798089</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>33.08686112852601</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.51630148144259</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>91.44685340747763</v>
+        <v>28.44613973055133</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>35.88287859022092</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.241664257226403</v>
+        <v>7.295309750508584</v>
       </c>
       <c r="C21" t="n">
-        <v>74.22705863657062</v>
+        <v>77.51266609915371</v>
       </c>
       <c r="D21" t="n">
-        <v>5.431248192919802</v>
+        <v>6.38339603169501</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.640140560897926</v>
+        <v>4.210715903514569</v>
       </c>
       <c r="C2" t="n">
-        <v>12.53397294011903</v>
+        <v>5.983752257384309</v>
       </c>
       <c r="D2" t="n">
-        <v>34.28066633689012</v>
+        <v>35.02188585359647</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74785507092459</v>
+        <v>18.07397523518378</v>
       </c>
       <c r="C3" t="n">
-        <v>37.1493331286993</v>
+        <v>29.07445826126929</v>
       </c>
       <c r="D3" t="n">
-        <v>68.24619166071703</v>
+        <v>101.404720371653</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.48486985937346</v>
+        <v>35.27615850899639</v>
       </c>
       <c r="C4" t="n">
-        <v>74.26626858315846</v>
+        <v>46.07341976030281</v>
       </c>
       <c r="D4" t="n">
-        <v>66.30233120630834</v>
+        <v>96.28196085089319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.0307626406637</v>
+        <v>40.10439371848221</v>
       </c>
       <c r="C5" t="n">
-        <v>115.1344620155447</v>
+        <v>52.76893910326607</v>
       </c>
       <c r="D5" t="n">
-        <v>42.60785036431157</v>
+        <v>55.51783267515714</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.82397372796611</v>
+        <v>35.50196048097316</v>
       </c>
       <c r="C6" t="n">
-        <v>154.9286234594849</v>
+        <v>59.00892751145879</v>
       </c>
       <c r="D6" t="n">
-        <v>35.58246379272141</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8781123582118</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>79.77681844709581</v>
+        <v>30.87596529856218</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.437225302760749</v>
+        <v>7.509540024555935</v>
       </c>
       <c r="C21" t="n">
-        <v>82.73913149321334</v>
+        <v>87.29840278546274</v>
       </c>
       <c r="D21" t="n">
-        <v>6.507572139915656</v>
+        <v>7.509540024555935</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_86_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626835271</v>
+        <v>10.84497639209647</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907171938261</v>
+        <v>37.7890721505649</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.883613991551134</v>
+        <v>1.040652566501619</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04622425755761</v>
+        <v>2.834305622160542</v>
       </c>
       <c r="D2" t="n">
-        <v>37.88073516836317</v>
+        <v>14.78021168743573</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06139244147782</v>
+        <v>7.706719478337462</v>
       </c>
       <c r="C3" t="n">
-        <v>25.68251994309656</v>
+        <v>36.02032326881547</v>
       </c>
       <c r="D3" t="n">
-        <v>105.4642471287136</v>
+        <v>69.42919764433444</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.94432778496097</v>
+        <v>11.00146477378976</v>
       </c>
       <c r="C4" t="n">
-        <v>60.98027690158638</v>
+        <v>138.9349716096001</v>
       </c>
       <c r="D4" t="n">
-        <v>123.874961826454</v>
+        <v>78.43967807391167</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.1238898038469</v>
+        <v>8.909360416039807</v>
       </c>
       <c r="C5" t="n">
-        <v>70.24404823885929</v>
+        <v>186.0902773399829</v>
       </c>
       <c r="D5" t="n">
-        <v>75.69274799742909</v>
+        <v>47.63930734857648</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.12210623488766</v>
+        <v>6.400013283984958</v>
       </c>
       <c r="C6" t="n">
-        <v>71.52719248830986</v>
+        <v>131.1398948378805</v>
       </c>
       <c r="D6" t="n">
-        <v>46.81267578160067</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.56024344842221</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>67.13288976410114</v>
+        <v>63.18037350680348</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>29.16477905005999</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14843349645307</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.710689521330387</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.38361901662985</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.674525711496686</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.525497063679301</v>
+        <v>0.673478925113312</v>
       </c>
       <c r="C2" t="n">
-        <v>6.367615609744812</v>
+        <v>6.90070461315083</v>
       </c>
       <c r="D2" t="n">
-        <v>39.45251324286232</v>
+        <v>12.41321797249667</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.91689560250429</v>
+        <v>5.546874528994479</v>
       </c>
       <c r="C3" t="n">
-        <v>32.57438882690916</v>
+        <v>22.02550974477719</v>
       </c>
       <c r="D3" t="n">
-        <v>109.7888457659208</v>
+        <v>65.29603980945535</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.86400439966198</v>
+        <v>13.03073727846791</v>
       </c>
       <c r="C4" t="n">
-        <v>61.96300635353744</v>
+        <v>113.894514665081</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4529745445439</v>
+        <v>93.69112865938585</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>12.49273953654066</v>
       </c>
       <c r="C5" t="n">
-        <v>91.35162388016572</v>
+        <v>221.8995248523854</v>
       </c>
       <c r="D5" t="n">
-        <v>99.89282890711299</v>
+        <v>63.02820261264524</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.97747052719389</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>90.2039608139012</v>
+        <v>212.9312595740908</v>
       </c>
       <c r="D6" t="n">
-        <v>57.60011955586462</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.51949307092936</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>85.15875936177682</v>
+        <v>123.2466432957361</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.45042657426681</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>67.09263810822702</v>
+        <v>55.15949476310704</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.896760132264616</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6191667690392</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.87095016533077</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.42714236680537</v>
+        <v>0.3720823799095411</v>
       </c>
       <c r="C2" t="n">
-        <v>7.591854996940584</v>
+        <v>3.083669539039231</v>
       </c>
       <c r="D2" t="n">
-        <v>35.70616400345649</v>
+        <v>8.587347169046851</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.60964962880404</v>
+        <v>4.800746273766903</v>
       </c>
       <c r="C3" t="n">
-        <v>28.54431450097601</v>
+        <v>25.74142480535137</v>
       </c>
       <c r="D3" t="n">
-        <v>113.7796501836841</v>
+        <v>63.36690557061038</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.83847895935156</v>
+        <v>14.14109393197106</v>
       </c>
       <c r="C4" t="n">
-        <v>70.92243590249383</v>
+        <v>102.3442529246172</v>
       </c>
       <c r="D4" t="n">
-        <v>160.899612996714</v>
+        <v>102.637795488187</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>12.19821522526662</v>
       </c>
       <c r="C5" t="n">
-        <v>100.5800523000858</v>
+        <v>252.3582473766427</v>
       </c>
       <c r="D5" t="n">
-        <v>121.2212977818749</v>
+        <v>69.55682484588652</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.21647718768238</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>113.6304245326386</v>
+        <v>254.7124783714265</v>
       </c>
       <c r="D6" t="n">
-        <v>72.13096732642167</v>
+        <v>36.46800022195202</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.86180422454201</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>105.7597531876919</v>
+        <v>110.4907953744573</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.71321616383547</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>87.12029127486194</v>
+        <v>43.64359419229195</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
         <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.067232489034337</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.94965890761</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09244467242221</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.27653405742811</v>
+        <v>0.6381360077604267</v>
       </c>
       <c r="C2" t="n">
-        <v>5.101161071266427</v>
+        <v>9.42772320388212</v>
       </c>
       <c r="D2" t="n">
-        <v>29.15299807760903</v>
+        <v>14.20098054193011</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.39781310886498</v>
+        <v>3.048326621686346</v>
       </c>
       <c r="C3" t="n">
-        <v>42.99564070748906</v>
+        <v>18.27523351455438</v>
       </c>
       <c r="D3" t="n">
-        <v>124.7015933934299</v>
+        <v>56.67138622764713</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.68760860806704</v>
+        <v>11.94590606527519</v>
       </c>
       <c r="C4" t="n">
-        <v>90.37282141903162</v>
+        <v>83.50647797552944</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5407920585784</v>
+        <v>109.6445288533965</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.91938318172731</v>
+        <v>16.10066234964769</v>
       </c>
       <c r="C5" t="n">
-        <v>67.88785374866696</v>
+        <v>223.3966901013617</v>
       </c>
       <c r="D5" t="n">
-        <v>76.84630154991909</v>
+        <v>87.05647767408593</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>69.63536466222628</v>
+        <v>327.5277238477082</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>47.49695393146069</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>61.26400198811371</v>
+        <v>223.0776220974815</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>46.06360228326034</v>
+        <v>85.53476873250335</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39568538254047</v>
+        <v>0.4005530633326986</v>
       </c>
       <c r="C2" t="n">
-        <v>2.717477645355171</v>
+        <v>4.544510122958485</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79988769924967</v>
+        <v>11.18701508989241</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.27571654063988</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="C3" t="n">
-        <v>31.6564547234384</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D3" t="n">
-        <v>120.3819034947439</v>
+        <v>55.87617058720721</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.62525978108076</v>
+        <v>9.891108120286615</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1573199501829</v>
+        <v>68.16568834896879</v>
       </c>
       <c r="D4" t="n">
-        <v>174.6961134844944</v>
+        <v>112.426801847232</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.03643214271093</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C5" t="n">
-        <v>114.4472386225719</v>
+        <v>203.1972310864836</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2735670899115</v>
+        <v>100.334615374024</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.44033135978387</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="C6" t="n">
-        <v>88.67439789068467</v>
+        <v>357.0724392593117</v>
       </c>
       <c r="D6" t="n">
-        <v>41.13719230334986</v>
+        <v>56.07055663264809</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>77.61304650693583</v>
+        <v>305.6013706210599</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>60.0829594999048</v>
+        <v>131.3480253511808</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.673519982842318</v>
+        <v>0.5311255079975244</v>
       </c>
       <c r="C2" t="n">
-        <v>7.937430188835462</v>
+        <v>13.47939597930871</v>
       </c>
       <c r="D2" t="n">
-        <v>20.79832511446867</v>
+        <v>11.76428273998953</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.74356822720911</v>
+        <v>2.051852701875834</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34672117051515</v>
+        <v>22.82072538521711</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1717273705771</v>
+        <v>52.21425165036661</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.23108023005904</v>
+        <v>7.746971134211581</v>
       </c>
       <c r="C4" t="n">
-        <v>89.63258365002955</v>
+        <v>68.26779011021046</v>
       </c>
       <c r="D4" t="n">
-        <v>190.2666320738488</v>
+        <v>114.0476673069435</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.00684084286328</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C5" t="n">
-        <v>151.6063892283137</v>
+        <v>168.4924497413589</v>
       </c>
       <c r="D5" t="n">
-        <v>137.2974164389165</v>
+        <v>113.9563647704485</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.99505987041232</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>132.4681994817264</v>
+        <v>344.3126643472159</v>
       </c>
       <c r="D6" t="n">
-        <v>60.01521890831177</v>
+        <v>69.9171262533451</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.14103717870882</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>102.2863298100667</v>
+        <v>396.9284508086194</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>80.36095833112266</v>
+        <v>239.3304553412874</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>54.47030787472577</v>
+        <v>89.52655489797087</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.325179474283947</v>
+        <v>0.3730641276137879</v>
       </c>
       <c r="C2" t="n">
-        <v>3.655046702910875</v>
+        <v>7.547676350249478</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3433339590459</v>
+        <v>8.658033003752621</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.20498964820511</v>
+        <v>2.915790681613027</v>
       </c>
       <c r="C3" t="n">
-        <v>26.34519964346316</v>
+        <v>35.45090960035233</v>
       </c>
       <c r="D3" t="n">
-        <v>106.8337851761379</v>
+        <v>56.41613182454296</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.11920204950392</v>
+        <v>11.8182788637231</v>
       </c>
       <c r="C4" t="n">
-        <v>84.02974950189299</v>
+        <v>98.43886055712343</v>
       </c>
       <c r="D4" t="n">
-        <v>203.5270983151105</v>
+        <v>116.5619231775195</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.14214209960009</v>
+        <v>10.55378782065321</v>
       </c>
       <c r="C5" t="n">
-        <v>178.8253443285565</v>
+        <v>274.1285027183157</v>
       </c>
       <c r="D5" t="n">
-        <v>148.4647965747239</v>
+        <v>104.0161692649496</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.59504658642736</v>
+        <v>6.078000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>159.1952989821416</v>
+        <v>332.2774192408543</v>
       </c>
       <c r="D6" t="n">
-        <v>57.9623844587317</v>
+        <v>58.88817254383644</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="C7" t="n">
-        <v>106.5382791171596</v>
+        <v>168.2813739849458</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>65.34021845614646</v>
+        <v>65.92435834017331</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.93680829402971</v>
+        <v>0.2140209995258046</v>
       </c>
       <c r="C2" t="n">
-        <v>5.068763397026282</v>
+        <v>3.39782880439821</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1913840490659</v>
+        <v>7.260024272905163</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82362957060084</v>
+        <v>2.110757564130642</v>
       </c>
       <c r="C3" t="n">
-        <v>20.10128424445344</v>
+        <v>32.29459073119883</v>
       </c>
       <c r="D3" t="n">
-        <v>94.87609813841175</v>
+        <v>50.66799901617789</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.76635371305181</v>
+        <v>8.257479940419922</v>
       </c>
       <c r="C4" t="n">
-        <v>75.63187963976578</v>
+        <v>90.37282141903162</v>
       </c>
       <c r="D4" t="n">
-        <v>209.4490004671273</v>
+        <v>113.0011242542164</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.53670686571608</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="C5" t="n">
-        <v>169.0324109786946</v>
+        <v>207.4432899073511</v>
       </c>
       <c r="D5" t="n">
-        <v>182.6787040677253</v>
+        <v>108.1640533153924</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="C6" t="n">
-        <v>215.9098821087756</v>
+        <v>314.7276972797383</v>
       </c>
       <c r="D6" t="n">
-        <v>82.11337798320324</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>2.395464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>160.915320959982</v>
+        <v>213.7353109438688</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>96.71687508387453</v>
+        <v>79.35957567279091</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.746930076482576</v>
+        <v>0.22776546738526</v>
       </c>
       <c r="C2" t="n">
-        <v>2.807798434145878</v>
+        <v>5.6479945425319</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6516027381794</v>
+        <v>10.22784758284327</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1448409963388</v>
+        <v>1.379355524466769</v>
       </c>
       <c r="C3" t="n">
-        <v>20.12091919853838</v>
+        <v>21.4217349066654</v>
       </c>
       <c r="D3" t="n">
-        <v>88.6420002164445</v>
+        <v>44.91495746929158</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.22282533779757</v>
+        <v>6.177156555120932</v>
       </c>
       <c r="C4" t="n">
-        <v>66.58311104972293</v>
+        <v>85.1018179949305</v>
       </c>
       <c r="D4" t="n">
-        <v>210.0871364748877</v>
+        <v>112.9755988139059</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.43348448804993</v>
+        <v>11.56007921750619</v>
       </c>
       <c r="C5" t="n">
-        <v>163.3873616792754</v>
+        <v>187.980141670658</v>
       </c>
       <c r="D5" t="n">
-        <v>205.9706683509809</v>
+        <v>123.7247544277043</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.19131160027045</v>
+        <v>9.821404033285093</v>
       </c>
       <c r="C6" t="n">
-        <v>243.8445312854143</v>
+        <v>323.6635648837927</v>
       </c>
       <c r="D6" t="n">
-        <v>101.5146761145287</v>
+        <v>79.73853028663019</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>211.1601867156295</v>
+        <v>335.4249023806695</v>
       </c>
       <c r="D7" t="n">
-        <v>48.68781389671206</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>126.591457724105</v>
+        <v>176.4102449761093</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>56.57812019574367</v>
+        <v>60.90468232835936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.895574890451343</v>
+        <v>0.0755945732270044</v>
       </c>
       <c r="C2" t="n">
-        <v>8.501935118777377</v>
+        <v>6.615997778919255</v>
       </c>
       <c r="D2" t="n">
-        <v>27.25724326070844</v>
+        <v>11.4658314378985</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.86580366415445</v>
+        <v>1.065196259107789</v>
       </c>
       <c r="C3" t="n">
-        <v>15.86995163914969</v>
+        <v>21.57390580082366</v>
       </c>
       <c r="D3" t="n">
-        <v>81.12181280191395</v>
+        <v>42.74038630438489</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.73936349895164</v>
+        <v>4.403138453546945</v>
       </c>
       <c r="C4" t="n">
-        <v>58.52983463178634</v>
+        <v>69.21223140169589</v>
       </c>
       <c r="D4" t="n">
-        <v>206.6284393128262</v>
+        <v>110.1550376596049</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.34160111447822</v>
+        <v>10.65196259107789</v>
       </c>
       <c r="C5" t="n">
-        <v>145.3968349989526</v>
+        <v>172.8612270252572</v>
       </c>
       <c r="D5" t="n">
-        <v>226.317389521496</v>
+        <v>133.1249886958675</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.58253021264619</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>253.6256836628253</v>
+        <v>313.7616575387594</v>
       </c>
       <c r="D6" t="n">
-        <v>128.6845438295592</v>
+        <v>97.57001383886501</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.87207936547421</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>267.5134866871006</v>
+        <v>394.9521926799706</v>
       </c>
       <c r="D7" t="n">
-        <v>61.20411537815465</v>
+        <v>52.22112388429633</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>2.920699420134261</v>
       </c>
       <c r="C8" t="n">
-        <v>185.673034565678</v>
+        <v>298.9127235120263</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>94.2968669929061</v>
+        <v>130.57342641253</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.966661635784614</v>
+        <v>1.532508166329271</v>
       </c>
       <c r="C2" t="n">
-        <v>3.821943812632833</v>
+        <v>21.95678740547991</v>
       </c>
       <c r="D2" t="n">
-        <v>6.62679700366597</v>
+        <v>9.188176764045899</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.790126975469435</v>
+        <v>0.0854120502694725</v>
       </c>
       <c r="C2" t="n">
-        <v>4.828235209485814</v>
+        <v>20.1925867809484</v>
       </c>
       <c r="D2" t="n">
-        <v>20.06201433628357</v>
+        <v>9.696722074845745</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.24930716361646</v>
+        <v>0.6823146544515333</v>
       </c>
       <c r="C3" t="n">
-        <v>23.41959148480766</v>
+        <v>23.29687302177681</v>
       </c>
       <c r="D3" t="n">
-        <v>91.93576376419256</v>
+        <v>41.75372986161685</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.16574510223102</v>
+        <v>3.267256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>83.76173237863361</v>
+        <v>62.10339627524473</v>
       </c>
       <c r="D4" t="n">
-        <v>212.7162568268606</v>
+        <v>105.87952640761</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.90804417763285</v>
+        <v>9.081166264282997</v>
       </c>
       <c r="C5" t="n">
-        <v>216.1563007825415</v>
+        <v>151.1891464540088</v>
       </c>
       <c r="D5" t="n">
-        <v>201.380997833627</v>
+        <v>140.3899217072939</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.25916569838794</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>225.8922927655571</v>
+        <v>298.788041553587</v>
       </c>
       <c r="D6" t="n">
-        <v>98.09328536522857</v>
+        <v>111.5373384271844</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>130.5528097107408</v>
+        <v>419.0864964934699</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>64.43799231594365</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5126461991954</v>
+        <v>394.878561602152</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>227.1999807076138</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>86.5508776063988</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>9.626036240139976</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.428884878035614</v>
+        <v>2.759692796637784</v>
       </c>
       <c r="C2" t="n">
-        <v>2.894192232119597</v>
+        <v>13.67280027704533</v>
       </c>
       <c r="D2" t="n">
-        <v>9.508226515630358</v>
+        <v>20.84250376115978</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.55378782065321</v>
+        <v>2.488730430265664</v>
       </c>
       <c r="C3" t="n">
-        <v>9.783115872819465</v>
+        <v>43.35397861953915</v>
       </c>
       <c r="D3" t="n">
-        <v>8.968265278294613</v>
+        <v>9.306968236259761</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39935767769673</v>
+        <v>11.67702959874737</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14957843029467</v>
+        <v>59.94208527356982</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576395020905498</v>
+        <v>0.7784686399164912</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.542947538177491</v>
+        <v>2.016509784522948</v>
       </c>
       <c r="C2" t="n">
-        <v>4.645630136495907</v>
+        <v>10.5577148114702</v>
       </c>
       <c r="D2" t="n">
-        <v>24.23444207933251</v>
+        <v>25.89752269032661</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.85584731839174</v>
+        <v>6.955682484588651</v>
       </c>
       <c r="C3" t="n">
-        <v>10.74522862298134</v>
+        <v>49.98077562320512</v>
       </c>
       <c r="D3" t="n">
-        <v>14.78512042595696</v>
+        <v>25.30945581548277</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.34155039008665</v>
+        <v>3.292781800043802</v>
       </c>
       <c r="C4" t="n">
-        <v>15.6981457909065</v>
+        <v>69.87589284976673</v>
       </c>
       <c r="D4" t="n">
-        <v>19.76945352041802</v>
+        <v>19.10579207234717</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44641566966819</v>
+        <v>13.62351706677844</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17474005183308</v>
+        <v>73.72726883197743</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251876983088041</v>
+        <v>1.60276671373864</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.730461349688632</v>
+        <v>2.512292375167588</v>
       </c>
       <c r="C2" t="n">
-        <v>3.763038950378024</v>
+        <v>6.566910393706914</v>
       </c>
       <c r="D2" t="n">
-        <v>35.61289797155305</v>
+        <v>24.07343545583604</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.71349390127595</v>
+        <v>7.01458734684346</v>
       </c>
       <c r="C3" t="n">
-        <v>15.19254572321939</v>
+        <v>44.47317100238051</v>
       </c>
       <c r="D3" t="n">
-        <v>30.73852061996763</v>
+        <v>40.94378800561323</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.01867856857647</v>
+        <v>9.278497552836605</v>
       </c>
       <c r="C4" t="n">
-        <v>22.14331946928681</v>
+        <v>103.5949994998277</v>
       </c>
       <c r="D4" t="n">
-        <v>22.55172651425348</v>
+        <v>27.93759441975148</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.21646752101981</v>
+        <v>3.828816046562561</v>
       </c>
       <c r="C5" t="n">
-        <v>19.07044915499429</v>
+        <v>78.22074833586463</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>27.04714925199963</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74562430274197</v>
+        <v>14.8232090464785</v>
       </c>
       <c r="C21" t="n">
-        <v>102.148308246726</v>
+        <v>87.29223105148449</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023687290822592</v>
+        <v>2.47053484107975</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.089380098815464</v>
+        <v>1.518763698469816</v>
       </c>
       <c r="C2" t="n">
-        <v>3.301617529382023</v>
+        <v>8.417504816212151</v>
       </c>
       <c r="D2" t="n">
-        <v>38.50807195137689</v>
+        <v>23.17808154956294</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67422399310608</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C3" t="n">
-        <v>14.84893402673301</v>
+        <v>33.33033455917921</v>
       </c>
       <c r="D3" t="n">
-        <v>50.96743206597316</v>
+        <v>50.13294651736337</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.95334344074844</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="C4" t="n">
-        <v>31.17932533917445</v>
+        <v>108.023663393685</v>
       </c>
       <c r="D4" t="n">
-        <v>32.11100391050467</v>
+        <v>41.13424706023711</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.1635763181775</v>
+        <v>8.958447801252147</v>
       </c>
       <c r="C5" t="n">
+        <v>139.7272420069273</v>
+      </c>
+      <c r="D5" t="n">
         <v>31.07231483941155</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.54593383901924</v>
+        <v>4.870450360768428</v>
       </c>
       <c r="C6" t="n">
-        <v>21.61513920440203</v>
+        <v>71.48694083243576</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07859585980969</v>
+        <v>16.04698152433718</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9413158473299</v>
+        <v>100.5047790208486</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887084137070359</v>
+        <v>3.378311899860459</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.137886646951058</v>
+        <v>1.238965602759475</v>
       </c>
       <c r="C2" t="n">
-        <v>7.011642103730719</v>
+        <v>9.725192758268904</v>
       </c>
       <c r="D2" t="n">
-        <v>44.9218297032213</v>
+        <v>26.7320082389364</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44427404613408</v>
+        <v>6.513896017677587</v>
       </c>
       <c r="C3" t="n">
-        <v>12.86089492563322</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D3" t="n">
-        <v>64.81007469585319</v>
+        <v>56.15105994439632</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>13.41361888312417</v>
       </c>
       <c r="C4" t="n">
-        <v>28.98413747247858</v>
+        <v>93.85704402140357</v>
       </c>
       <c r="D4" t="n">
-        <v>42.93379060212151</v>
+        <v>55.28810371236337</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.21833320543707</v>
+        <v>13.13087554430109</v>
       </c>
       <c r="C5" t="n">
-        <v>33.67394625566561</v>
+        <v>170.7504694611265</v>
       </c>
       <c r="D5" t="n">
-        <v>29.18245050873644</v>
+        <v>37.65002445786519</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>8.251589454194443</v>
       </c>
       <c r="C6" t="n">
-        <v>24.71451670670921</v>
+        <v>146.3952724141716</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>17.0676838383308</v>
+        <v>59.40751707938298</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069037042585524</v>
+        <v>17.28801509514587</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15585190456247</v>
+        <v>113.2364988732055</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301777781939143</v>
+        <v>4.322003773786468</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.842961425049515</v>
+        <v>2.363066724122073</v>
       </c>
       <c r="C2" t="n">
-        <v>8.533351045313276</v>
+        <v>8.1102177847829</v>
       </c>
       <c r="D2" t="n">
-        <v>42.22595050735956</v>
+        <v>26.2558606023767</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69876768571225</v>
+        <v>5.301437602932776</v>
       </c>
       <c r="C3" t="n">
-        <v>22.39366513386975</v>
+        <v>35.15638528907828</v>
       </c>
       <c r="D3" t="n">
-        <v>88.05786033241766</v>
+        <v>62.91530162665685</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>12.76272015520853</v>
       </c>
       <c r="C4" t="n">
-        <v>31.11551173839841</v>
+        <v>87.06727689883262</v>
       </c>
       <c r="D4" t="n">
-        <v>68.14016290865837</v>
+        <v>68.40818003191774</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.08489763311751</v>
+        <v>16.29701189049706</v>
       </c>
       <c r="C5" t="n">
-        <v>46.09305471438775</v>
+        <v>171.683129780161</v>
       </c>
       <c r="D5" t="n">
-        <v>39.04901493641689</v>
+        <v>46.68210333693584</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.54721868635975</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>41.70071548558752</v>
+        <v>203.9953919700363</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08686112852601</v>
+        <v>39.24536447726626</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>28.44613973055133</v>
+        <v>127.0793863331156</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>21.44627859927157</v>
+        <v>49.23464736797754</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>38.93905919354123</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295309750508584</v>
+        <v>17.65601659579914</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51266609915371</v>
+        <v>125.3577178301739</v>
       </c>
       <c r="D21" t="n">
-        <v>6.38339603169501</v>
+        <v>5.296804978739742</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.210715903514569</v>
+        <v>2.089159114637213</v>
       </c>
       <c r="C2" t="n">
-        <v>5.983752257384309</v>
+        <v>5.255295460833175</v>
       </c>
       <c r="D2" t="n">
-        <v>35.02188585359647</v>
+        <v>21.15666302651876</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.07397523518378</v>
+        <v>7.701810739816228</v>
       </c>
       <c r="C3" t="n">
-        <v>29.07445826126929</v>
+        <v>52.44987109938585</v>
       </c>
       <c r="D3" t="n">
-        <v>101.404720371653</v>
+        <v>67.21044783273663</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.27615850899639</v>
+        <v>7.823547455142831</v>
       </c>
       <c r="C4" t="n">
-        <v>46.07341976030281</v>
+        <v>136.6887328622834</v>
       </c>
       <c r="D4" t="n">
-        <v>96.28196085089319</v>
+        <v>62.5118033202114</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.10439371848221</v>
+        <v>6.945865007546185</v>
       </c>
       <c r="C5" t="n">
-        <v>52.76893910326607</v>
+        <v>121.8839774822415</v>
       </c>
       <c r="D5" t="n">
-        <v>55.51783267515714</v>
+        <v>36.44738352016284</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.50196048097316</v>
+        <v>4.910702016642547</v>
       </c>
       <c r="C6" t="n">
-        <v>59.00892751145879</v>
+        <v>83.68319256229388</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>24.91577498607981</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>46.53189593818607</v>
+        <v>34.61446055633404</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>27.24840753137022</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>30.87596529856218</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.509540024555935</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.29840278546274</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.509540024555935</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
